--- a/data/trans_orig/IP37-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Clase-trans_orig.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20833</t>
+          <t>21349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16307</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23638</t>
+          <t>23574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37089</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44861</t>
+          <t>44723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65820</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72123</t>
+          <t>71621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69458</t>
+          <t>69077</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138153</t>
+          <t>137649</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146661</t>
+          <t>146768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12584</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55316</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110557</t>
+          <t>111033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116555</t>
+          <t>116561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7281</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61845</t>
+          <t>61831</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>68719</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68849</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127471</t>
+          <t>127145</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136129</t>
+          <t>136592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173979</t>
+          <t>171603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>195315</t>
+          <t>195323</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186872</t>
+          <t>189211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211398</t>
+          <t>212859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368608</t>
+          <t>367895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402406</t>
+          <t>401687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64008</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>87720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68175</t>
+          <t>66714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>90362</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136490</t>
+          <t>137209</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>170288</t>
+          <t>171001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>17255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22566</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41337</t>
+          <t>41363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,16%</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33691</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>34169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39163</t>
+          <t>39117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69802</t>
+          <t>69561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>76016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>61836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68966</t>
+          <t>68965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110974</t>
+          <t>111011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118551</t>
+          <t>118540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111646</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119308</t>
+          <t>119357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226136</t>
+          <t>226072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236664</t>
+          <t>236824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89157</t>
+          <t>89114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95859</t>
+          <t>95937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87005</t>
+          <t>87000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92196</t>
+          <t>92192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179015</t>
+          <t>179119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187313</t>
+          <t>187298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2251</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>13933</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>41286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47157</t>
+          <t>47144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54103</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61678</t>
+          <t>61771</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98725</t>
+          <t>98783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>108036</t>
+          <t>108011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>287082</t>
+          <t>288285</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310966</t>
+          <t>310846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>289809</t>
+          <t>290883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315153</t>
+          <t>316497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586970</t>
+          <t>585044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>620445</t>
+          <t>619973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,09%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70091</t>
+          <t>68888</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64944</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>89214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>116825</t>
+          <t>117297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>150300</t>
+          <t>152226</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106172</t>
+          <t>105964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90237</t>
+          <t>90819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95438</t>
+          <t>95442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199387</t>
+          <t>198933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204619</t>
+          <t>204564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81349</t>
+          <t>80217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165825</t>
+          <t>165555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49874</t>
+          <t>50087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>55781</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>59332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65034</t>
+          <t>65030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111152</t>
+          <t>111902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119451</t>
+          <t>119702</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>261540</t>
+          <t>264542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>286229</t>
+          <t>286985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>256438</t>
+          <t>254529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280760</t>
+          <t>279497</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526878</t>
+          <t>526225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>559849</t>
+          <t>560899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44612</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69301</t>
+          <t>66299</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53345</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>77667</t>
+          <t>79576</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105096</t>
+          <t>104046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138067</t>
+          <t>138720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>12831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13574</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>23034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30347</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>746</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8287</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85573</t>
+          <t>85424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>92395</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>60552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148457</t>
+          <t>149205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158096</t>
+          <t>158574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48358</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47466</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56900</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94825</t>
+          <t>94603</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>104011</t>
+          <t>104324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>64601</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126297</t>
+          <t>126067</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132056</t>
+          <t>132060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>163703</t>
+          <t>161076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>202932</t>
+          <t>201949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159916</t>
+          <t>160267</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188770</t>
+          <t>187799</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>330986</t>
+          <t>329948</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>381394</t>
+          <t>379018</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>52850</t>
+          <t>53833</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92079</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>62541</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91395</t>
+          <t>91044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125698</t>
+          <t>128074</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>176106</t>
+          <t>177144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
